--- a/Excel/PetFeeConfig.xlsx
+++ b/Excel/PetFeeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="宠物" sheetId="2" r:id="rId1"/>
@@ -1017,7 +1017,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:G55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="11.375" style="1" customWidth="1"/>
@@ -1085,13 +1085,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="3:7">
@@ -1099,102 +1099,52 @@
         <v>2</v>
       </c>
       <c r="D7" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>200</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="3:7">
-      <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="D8" s="3">
-        <v>100</v>
-      </c>
-      <c r="E8" s="3">
-        <v>149</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>300</v>
-      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="3:7">
-      <c r="C9" s="3">
-        <v>4</v>
-      </c>
-      <c r="D9" s="3">
-        <v>150</v>
-      </c>
-      <c r="E9" s="3">
-        <v>199</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>400</v>
-      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="3:7">
-      <c r="C10" s="3">
-        <v>5</v>
-      </c>
-      <c r="D10" s="3">
-        <v>200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>249</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>500</v>
-      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="3:7">
-      <c r="C11" s="3">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3">
-        <v>250</v>
-      </c>
-      <c r="E11" s="3">
-        <v>299</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>600</v>
-      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="3:7">
-      <c r="C12" s="3">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3">
-        <v>300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>349</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>700</v>
-      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="3:7">
       <c r="C13" s="3"/>
